--- a/Data/solar_prevalence_csiro_24.xlsx
+++ b/Data/solar_prevalence_csiro_24.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E1A220D0-995B-4DF7-9C35-080FD36AC134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{440BC8B3-3FD2-4D72-AFCC-1EB984B127E1}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{E1A220D0-995B-4DF7-9C35-080FD36AC134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324EBF56-7295-446E-B182-51F5FBAE0148}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{A0DDE90D-8409-47C8-90CE-1E5B9CFF4EA4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{A0DDE90D-8409-47C8-90CE-1E5B9CFF4EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>state</t>
   </si>
@@ -97,6 +98,18 @@
   </si>
   <si>
     <t>table A-1</t>
+  </si>
+  <si>
+    <t>pct_of_pv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportion of PV systems with a battery </t>
+  </si>
+  <si>
+    <t>Figure 5-8</t>
+  </si>
+  <si>
+    <t>Scraped with webplotdigitiser</t>
   </si>
 </sst>
 </file>
@@ -734,4 +747,133 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF5A529-99FF-4191-A4C1-3701B108F510}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2024.9399074252201</v>
+      </c>
+      <c r="B2">
+        <v>0.132391042327131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2029.43071578329</v>
+      </c>
+      <c r="B3">
+        <v>0.18552187256282199</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2033.9596276751899</v>
+      </c>
+      <c r="B4">
+        <v>0.25258307927601198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2038.88883937162</v>
+      </c>
+      <c r="B5">
+        <v>0.272849054501625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2043.4443690431499</v>
+      </c>
+      <c r="B6">
+        <v>0.27930660076369102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2048.2282768330101</v>
+      </c>
+      <c r="B7">
+        <v>0.28999118817797798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050.0391366440099</v>
+      </c>
+      <c r="B8">
+        <v>0.29668553949620602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2036.1672017907199</v>
+      </c>
+      <c r="B9">
+        <v>0.26699273784323002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2031.90531849165</v>
+      </c>
+      <c r="B10">
+        <v>0.22163818861350501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2045.87758657361</v>
+      </c>
+      <c r="B11">
+        <v>0.28019710121440999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2052.1855749460601</v>
+      </c>
+      <c r="B12">
+        <v>0.303257943300483</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2053.2646889021598</v>
+      </c>
+      <c r="B13">
+        <v>0.30590817473741699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/solar_prevalence_csiro_24.xlsx
+++ b/Data/solar_prevalence_csiro_24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{E1A220D0-995B-4DF7-9C35-080FD36AC134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324EBF56-7295-446E-B182-51F5FBAE0148}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{E1A220D0-995B-4DF7-9C35-080FD36AC134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA0E7B75-19B6-43EE-87F6-C2386B7E1E2E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{A0DDE90D-8409-47C8-90CE-1E5B9CFF4EA4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{A0DDE90D-8409-47C8-90CE-1E5B9CFF4EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>state</t>
   </si>
@@ -106,17 +106,20 @@
     <t xml:space="preserve">Proportion of PV systems with a battery </t>
   </si>
   <si>
-    <t>Figure 5-8</t>
-  </si>
-  <si>
     <t>Scraped with webplotdigitiser</t>
+  </si>
+  <si>
+    <t>Figure 5-7</t>
+  </si>
+  <si>
+    <t>https://publications.csiro.au/publications/publication/PIcsiro:EP2022-5296</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +129,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -147,16 +157,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -491,15 +504,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0B2278-6F8D-4BD9-BA49-DEA77CDF5D7A}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -542,7 +555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -559,7 +572,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -576,7 +589,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -593,7 +606,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -610,7 +623,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -627,7 +640,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -644,7 +657,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -669,9 +682,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23FB138-B45E-45C8-837A-3937EEA5B4CF}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -681,11 +694,11 @@
       <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -696,7 +709,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -704,7 +717,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -712,7 +725,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -720,7 +733,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -728,7 +741,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -736,7 +749,7 @@
         <v>0.155</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -745,16 +758,19 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F1" r:id="rId1" xr:uid="{23782E68-5371-42B0-8BBC-89922D456BBF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF5A529-99FF-4191-A4C1-3701B108F510}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -768,112 +784,139 @@
         <v>13</v>
       </c>
       <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>2.1996303142329001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2020.9705042816299</v>
+      </c>
+      <c r="B3">
+        <v>3.2347504621071999E-2</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2024.9399074252201</v>
-      </c>
-      <c r="B2">
-        <v>0.132391042327131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2029.43071578329</v>
-      </c>
-      <c r="B3">
-        <v>0.18552187256282199</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2033.9596276751899</v>
+        <v>2022.026641294</v>
       </c>
       <c r="B4">
-        <v>0.25258307927601198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>3.4935304990757803E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>2038.88883937162</v>
+        <v>2023.0256898192099</v>
       </c>
       <c r="B5">
-        <v>0.272849054501625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>5.5637707948243902E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>2043.4443690431499</v>
+        <v>2023.9961941008501</v>
       </c>
       <c r="B6">
-        <v>0.27930660076369102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>9.3160813308687501E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>2048.2282768330101</v>
+        <v>2029.96194100856</v>
       </c>
       <c r="B7">
-        <v>0.28999118817797798</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.21478743068391801</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>2050.0391366440099</v>
+        <v>2030.9039010466199</v>
       </c>
       <c r="B8">
-        <v>0.29668553949620602</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.23290203327171899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>2036.1672017907199</v>
+        <v>2033.07326355851</v>
       </c>
       <c r="B9">
-        <v>0.26699273784323002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.26913123844731901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>2031.90531849165</v>
+        <v>2036.013320647</v>
       </c>
       <c r="B10">
-        <v>0.22163818861350501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.309242144177449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>2045.87758657361</v>
+        <v>2041.0371075166499</v>
       </c>
       <c r="B11">
-        <v>0.28019710121440999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.37652495378927903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>2052.1855749460601</v>
+        <v>2044.2055185537499</v>
       </c>
       <c r="B12">
-        <v>0.303257943300483</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.41534195933456503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>2053.2646889021598</v>
+        <v>2046.40342530922</v>
       </c>
       <c r="B13">
-        <v>0.30590817473741699</v>
+        <v>0.44121996303142302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2047.4595623215901</v>
+      </c>
+      <c r="B14">
+        <v>0.45415896487985202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2048.43006660323</v>
+      </c>
+      <c r="B15">
+        <v>0.46451016635859499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2050.0285442435702</v>
+      </c>
+      <c r="B16">
+        <v>0.47874306839186598</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K1" r:id="rId1" xr:uid="{9330BD82-4EDE-4160-A72D-303164129D3B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>